--- a/etf_holdings/2026-08-21_common_holdings_all_00981A_00991A_00980A_00982A_00403A_00985A.xlsx
+++ b/etf_holdings/2026-08-21_common_holdings_all_00981A_00991A_00980A_00982A_00403A_00985A.xlsx
@@ -590,11 +590,11 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>7.87%</t>
+          <t>8.98%</t>
         </is>
       </c>
       <c r="M2" t="n">
-        <v>663000</v>
+        <v>753000</v>
       </c>
       <c r="N2" t="inlineStr">
         <is>
@@ -629,7 +629,7 @@
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>13.60%</t>
+          <t>13.69%</t>
         </is>
       </c>
       <c r="V2" t="n">
@@ -637,12 +637,12 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>68.85%</t>
+          <t>70.05%</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
         <is>
-          <t>11.47%</t>
+          <t>11.67%</t>
         </is>
       </c>
     </row>
@@ -698,7 +698,7 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>4.04%</t>
+          <t>4.09%</t>
         </is>
       </c>
       <c r="M3" t="n">
@@ -737,7 +737,7 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>1.33%</t>
+          <t>1.35%</t>
         </is>
       </c>
       <c r="V3" t="n">
@@ -745,12 +745,12 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>35.07%</t>
+          <t>35.14%</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>5.84%</t>
+          <t>5.86%</t>
         </is>
       </c>
     </row>
@@ -806,11 +806,11 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>4.93%</t>
+          <t>4.62%</t>
         </is>
       </c>
       <c r="M4" t="n">
-        <v>254000</v>
+        <v>249000</v>
       </c>
       <c r="N4" t="inlineStr">
         <is>
@@ -845,7 +845,7 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>1.89%</t>
+          <t>1.81%</t>
         </is>
       </c>
       <c r="V4" t="n">
@@ -853,12 +853,12 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>28.77%</t>
+          <t>28.38%</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>4.79%</t>
+          <t>4.73%</t>
         </is>
       </c>
     </row>
@@ -914,7 +914,7 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>1.67%</t>
+          <t>1.65%</t>
         </is>
       </c>
       <c r="M5" t="n">
@@ -953,7 +953,7 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>3.33%</t>
+          <t>3.29%</t>
         </is>
       </c>
       <c r="V5" t="n">
@@ -961,12 +961,12 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>23.04%</t>
+          <t>22.98%</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>3.84%</t>
+          <t>3.83%</t>
         </is>
       </c>
     </row>
@@ -1022,7 +1022,7 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>2.10%</t>
+          <t>2.01%</t>
         </is>
       </c>
       <c r="M6" t="n">
@@ -1061,7 +1061,7 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>2.07%</t>
+          <t>1.99%</t>
         </is>
       </c>
       <c r="V6" t="n">
@@ -1069,12 +1069,12 @@
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>22.10%</t>
+          <t>21.93%</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>3.68%</t>
+          <t>3.65%</t>
         </is>
       </c>
     </row>
@@ -1130,7 +1130,7 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>1.87%</t>
+          <t>1.84%</t>
         </is>
       </c>
       <c r="M7" t="n">
@@ -1169,7 +1169,7 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>2.59%</t>
+          <t>2.56%</t>
         </is>
       </c>
       <c r="V7" t="n">
@@ -1177,12 +1177,12 @@
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>19.94%</t>
+          <t>19.88%</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>3.32%</t>
+          <t>3.31%</t>
         </is>
       </c>
     </row>
@@ -1238,7 +1238,7 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>1.21%</t>
+          <t>1.22%</t>
         </is>
       </c>
       <c r="M8" t="n">
@@ -1281,7 +1281,7 @@
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>12.08%</t>
+          <t>12.09%</t>
         </is>
       </c>
       <c r="X8" t="inlineStr">
@@ -1402,12 +1402,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>3008</t>
+          <t>2360</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>大立光</t>
+          <t>致茂</t>
         </is>
       </c>
       <c r="D10" t="n">
@@ -1415,20 +1415,20 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>大立光</t>
+          <t>致茂</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>0.00%</t>
+          <t>0.22%</t>
         </is>
       </c>
       <c r="G10" t="n">
-        <v>1000</v>
+        <v>294000</v>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>大立光電</t>
+          <t>致茂電子</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1437,64 +1437,64 @@
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>大立光電</t>
+          <t>致茂電子</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>0.73%</t>
+          <t>1.59%</t>
         </is>
       </c>
       <c r="M10" t="n">
-        <v>26000</v>
+        <v>148000</v>
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>大立光</t>
+          <t>致茂</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>2.86%</t>
+          <t>3.65%</t>
         </is>
       </c>
       <c r="P10" t="n">
-        <v>257000</v>
+        <v>844000</v>
       </c>
       <c r="Q10" t="inlineStr">
         <is>
-          <t>大立光</t>
+          <t>致茂</t>
         </is>
       </c>
       <c r="R10" t="inlineStr">
         <is>
-          <t>2.02%</t>
+          <t>1.25%</t>
         </is>
       </c>
       <c r="S10" t="n">
-        <v>626000</v>
+        <v>1000000</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>大立光電</t>
+          <t>致茂電子</t>
         </is>
       </c>
       <c r="U10" t="inlineStr">
         <is>
-          <t>2.24%</t>
+          <t>0.10%</t>
         </is>
       </c>
       <c r="V10" t="n">
-        <v>41000</v>
+        <v>5000</v>
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>7.85%</t>
+          <t>6.81%</t>
         </is>
       </c>
       <c r="X10" t="inlineStr">
         <is>
-          <t>1.57%</t>
+          <t>1.36%</t>
         </is>
       </c>
     </row>
@@ -1506,12 +1506,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2360</t>
+          <t>3008</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>致茂</t>
+          <t>大立光</t>
         </is>
       </c>
       <c r="D11" t="n">
@@ -1519,20 +1519,20 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>致茂</t>
+          <t>大立光</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>0.22%</t>
+          <t>0.00%</t>
         </is>
       </c>
       <c r="G11" t="n">
-        <v>294000</v>
+        <v>1000</v>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>致茂電子</t>
+          <t>大立光電</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1541,64 +1541,64 @@
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>致茂電子</t>
+          <t>大立光電</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>1.59%</t>
+          <t>0.72%</t>
         </is>
       </c>
       <c r="M11" t="n">
-        <v>148000</v>
+        <v>26000</v>
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>致茂</t>
+          <t>大立光</t>
         </is>
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>3.65%</t>
+          <t>2.86%</t>
         </is>
       </c>
       <c r="P11" t="n">
-        <v>844000</v>
+        <v>257000</v>
       </c>
       <c r="Q11" t="inlineStr">
         <is>
-          <t>致茂</t>
+          <t>大立光</t>
         </is>
       </c>
       <c r="R11" t="inlineStr">
         <is>
+          <t>2.02%</t>
+        </is>
+      </c>
+      <c r="S11" t="n">
+        <v>626000</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>大立光電</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>0.65%</t>
+        </is>
+      </c>
+      <c r="V11" t="n">
+        <v>12000</v>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>6.25%</t>
+        </is>
+      </c>
+      <c r="X11" t="inlineStr">
+        <is>
           <t>1.25%</t>
-        </is>
-      </c>
-      <c r="S11" t="n">
-        <v>1000000</v>
-      </c>
-      <c r="T11" t="inlineStr">
-        <is>
-          <t>致茂電子</t>
-        </is>
-      </c>
-      <c r="U11" t="inlineStr">
-        <is>
-          <t>0.10%</t>
-        </is>
-      </c>
-      <c r="V11" t="n">
-        <v>5000</v>
-      </c>
-      <c r="W11" t="inlineStr">
-        <is>
-          <t>6.81%</t>
-        </is>
-      </c>
-      <c r="X11" t="inlineStr">
-        <is>
-          <t>1.36%</t>
         </is>
       </c>
     </row>
